--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488164_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488164_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>15.3008</v>
+        <v>15.669</v>
       </c>
       <c r="E2" t="n">
-        <v>13.0949</v>
+        <v>13.2907</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2059</v>
+        <v>2.3783</v>
       </c>
       <c r="G2" t="n">
         <v>16.5785</v>
@@ -610,13 +610,13 @@
         <v>2.594</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.778</v>
+        <v>-0.4098</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7996</v>
+        <v>-0.6037</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0216</v>
+        <v>0.194</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3144</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.756</v>
+        <v>10.7325</v>
       </c>
       <c r="E3" t="n">
-        <v>9.1694</v>
+        <v>8.9735</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5866</v>
+        <v>1.759</v>
       </c>
       <c r="G3" t="n">
         <v>8.5639</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0492</v>
+        <v>-0.0727</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0721</v>
+        <v>-0.1237</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1214</v>
+        <v>0.051</v>
       </c>
       <c r="V3" t="n">
         <v>0.9444</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.8969</v>
+        <v>3.6478</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3005</v>
+        <v>3.1254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5964</v>
+        <v>0.5225</v>
       </c>
       <c r="G4" t="n">
         <v>1.2362</v>
@@ -766,13 +766,13 @@
         <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0312</v>
+        <v>0.7822</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3779</v>
+        <v>0.2027</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6533</v>
+        <v>0.5795</v>
       </c>
       <c r="V4" t="n">
         <v>1.2589</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0666</v>
+        <v>3.3862</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7497</v>
+        <v>0.8477</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3169</v>
+        <v>2.5385</v>
       </c>
       <c r="G5" t="n">
         <v>3.3442</v>
@@ -844,13 +844,13 @@
         <v>0.9264</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0187</v>
+        <v>-0.6992</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6566</v>
+        <v>-0.5586</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3621</v>
+        <v>-0.1405</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9161</v>
+        <v>0.9539</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0449</v>
+        <v>-0.9433</v>
       </c>
       <c r="F7" t="n">
-        <v>1.961</v>
+        <v>1.8972</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1495</v>
+        <v>2.4291</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5919</v>
+        <v>1.4798</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5576</v>
+        <v>0.9493</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2645</v>
+        <v>1.5528</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7514999999999999</v>
+        <v>1.3869</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.487</v>
+        <v>0.1659</v>
       </c>
       <c r="M7" t="n">
-        <v>0.885</v>
+        <v>0.8763</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1596</v>
+        <v>0.0929</v>
       </c>
       <c r="O7" t="n">
-        <v>1.0446</v>
+        <v>0.7834</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297</v>
+        <v>0.9264</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0249</v>
+        <v>-0.2338</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.383</v>
+        <v>-0.3283</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4079</v>
+        <v>0.0945</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6289</v>
+        <v>-0.315</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9046</v>
+        <v>0.7678</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9433</v>
+        <v>-0.947</v>
       </c>
       <c r="F8" t="n">
-        <v>1.848</v>
+        <v>1.7148</v>
       </c>
       <c r="G8" t="n">
-        <v>2.4291</v>
+        <v>1.1495</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4798</v>
+        <v>0.5919</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9493</v>
+        <v>0.5576</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5528</v>
+        <v>0.2645</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3869</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1659</v>
+        <v>-0.487</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8763</v>
+        <v>0.885</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0929</v>
+        <v>-0.1596</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7834</v>
+        <v>1.0446</v>
       </c>
       <c r="P8" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9264</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.8529</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>1.297</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.283</v>
+        <v>-0.1234</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3283</v>
+        <v>-0.2851</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0453</v>
+        <v>0.1616</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.315</v>
+        <v>-0.6289</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3755</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6319</v>
+        <v>0.7299</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2564</v>
+        <v>-0.0348</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1653</v>
@@ -1156,13 +1156,13 @@
         <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4417</v>
+        <v>-0.1222</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1134</v>
+        <v>0.1082</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>I. VAZQUEZ FLORES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.189</v>
+        <v>-0.2083</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1917</v>
+        <v>-2.0616</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0028</v>
+        <v>1.8532</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0754</v>
+        <v>-1.7669</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5854</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.51</v>
+        <v>-2.3733</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0179</v>
+        <v>-0.9406</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7904</v>
+        <v>1.4943</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.2275</v>
+        <v>-2.4349</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0575</v>
+        <v>-0.8263</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.795</v>
+        <v>-0.8878</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.0616</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>-2.0382</v>
       </c>
       <c r="R10" t="n">
         <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>0.572</v>
+        <v>0.1694</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6354</v>
+        <v>-0.3416</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2074</v>
+        <v>0.5111</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>1.5744</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ FLORES</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5514</v>
+        <v>-0.2897</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3553</v>
+        <v>-2.8</v>
       </c>
       <c r="F11" t="n">
-        <v>1.804</v>
+        <v>2.5103</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7669</v>
+        <v>-1.0754</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6064000000000001</v>
+        <v>-1.5854</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3733</v>
+        <v>0.51</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9406</v>
+        <v>-1.0179</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4943</v>
+        <v>-0.7904</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.4349</v>
+        <v>-0.2275</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8263</v>
+        <v>-0.0575</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8878</v>
+        <v>-0.795</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0616</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.0382</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
         <v>1.8529</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1736</v>
+        <v>0.4713</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6354</v>
+        <v>-0.2437</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4618</v>
+        <v>0.715</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5744</v>
+        <v>0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3428</v>
+        <v>-4.4419</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4874</v>
+        <v>-3.3895</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8554</v>
+        <v>-1.0524</v>
       </c>
       <c r="G12" t="n">
         <v>0.0253</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3676</v>
+        <v>-0.4666</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8207</v>
+        <v>-0.7228</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4531</v>
+        <v>0.2561</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5183</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5408</v>
+        <v>-6.3198</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3848</v>
+        <v>-5.2868</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1561</v>
+        <v>-1.033</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9374</v>
@@ -1468,13 +1468,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2126</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0485</v>
+        <v>0.0746</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3144</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.7808</v>
+        <v>26.78089999999999</v>
       </c>
       <c r="E14" t="n">
         <v>13.7273</v>
       </c>
       <c r="F14" t="n">
-        <v>13.0537</v>
+        <v>13.0536</v>
       </c>
       <c r="G14" t="n">
         <v>30.57</v>
@@ -1519,10 +1519,10 @@
         <v>28.1471</v>
       </c>
       <c r="J14" t="n">
-        <v>29.57970000000001</v>
+        <v>29.5797</v>
       </c>
       <c r="K14" t="n">
-        <v>8.9221</v>
+        <v>8.922099999999999</v>
       </c>
       <c r="L14" t="n">
         <v>20.65750000000001</v>
@@ -1546,13 +1546,13 @@
         <v>15.7494</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6962999999999998</v>
+        <v>-0.6964000000000001</v>
       </c>
       <c r="T14" t="n">
         <v>-3.3014</v>
       </c>
       <c r="U14" t="n">
-        <v>2.605</v>
+        <v>2.605099999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3132999999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2208</v>
+        <v>1.3503</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7916</v>
+        <v>1.9874</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5707</v>
+        <v>-0.6371</v>
       </c>
       <c r="G15" t="n">
         <v>1.7842</v>
@@ -1624,13 +1624,13 @@
         <v>2.4087</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4347</v>
+        <v>-0.3053</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8754</v>
+        <v>-0.6796</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4407</v>
+        <v>0.3743</v>
       </c>
       <c r="V15" t="n">
         <v>-0.3139</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.1212</v>
       </c>
       <c r="E16" t="n">
-        <v>3.392</v>
+        <v>2.9023</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6162</v>
+        <v>-2.7811</v>
       </c>
       <c r="G16" t="n">
         <v>-3.2253</v>
@@ -1702,13 +1702,13 @@
         <v>0.7411</v>
       </c>
       <c r="S16" t="n">
-        <v>1.243</v>
+        <v>0.5885</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5944</v>
+        <v>0.1048</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6486</v>
+        <v>0.4837</v>
       </c>
       <c r="V16" t="n">
         <v>2.2022</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1763</v>
+        <v>-0.6419</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6955</v>
+        <v>0.3037</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8718</v>
+        <v>-0.9456</v>
       </c>
       <c r="G17" t="n">
         <v>-3.3767</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2565</v>
+        <v>0.7909</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6156</v>
+        <v>0.2239</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6409</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>1.5733</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.323</v>
+        <v>-0.9307</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7536</v>
+        <v>-1.4599</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4307</v>
+        <v>0.5292</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4543</v>
@@ -1858,13 +1858,13 @@
         <v>2.4087</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3509</v>
+        <v>0.0414</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6901</v>
+        <v>-0.3964</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3392</v>
+        <v>0.4377</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GALLEGO GOMEZ</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1468</v>
+        <v>-2.1938</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.7713</v>
+        <v>-1.6371</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6245</v>
+        <v>-0.5566</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6403</v>
+        <v>-0.4609</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7387</v>
+        <v>0.9922</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9015</v>
+        <v>-1.4531</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7147</v>
+        <v>2.0941</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1033</v>
+        <v>2.1035</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.0094</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9255</v>
+        <v>-2.555</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6354</v>
+        <v>-1.1113</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2901</v>
+        <v>-1.4437</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1853</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.9646</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1499</v>
+        <v>2.594</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3082</v>
+        <v>-0.1029</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.092</v>
+        <v>-0.4511</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4002</v>
+        <v>0.3482</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.2594</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>A. GALLEGO GOMEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6107</v>
+        <v>-2.3673</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9309</v>
+        <v>-3.9672</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6797</v>
+        <v>1.5999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4609</v>
+        <v>-2.6403</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9922</v>
+        <v>-0.7387</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4531</v>
+        <v>-1.9015</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0941</v>
+        <v>-0.7147</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1035</v>
+        <v>-0.1033</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0094</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.555</v>
+        <v>-1.9255</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1113</v>
+        <v>-0.6354</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4437</v>
+        <v>-1.2901</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.9646</v>
       </c>
       <c r="R20" t="n">
-        <v>2.594</v>
+        <v>3.1499</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5198</v>
+        <v>0.0877</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7449</v>
+        <v>-0.2879</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2251</v>
+        <v>0.3755</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2594</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9094</v>
+        <v>-3.6131</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3921</v>
+        <v>-0.0975</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3015</v>
+        <v>-3.5156</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4317</v>
@@ -2092,13 +2092,13 @@
         <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1344</v>
+        <v>0.4306</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3756</v>
+        <v>-0.1141</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7588</v>
+        <v>0.5446</v>
       </c>
       <c r="V21" t="n">
         <v>0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1758</v>
+        <v>-4.7251</v>
       </c>
       <c r="E22" t="n">
         <v>-1.8006</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3752</v>
+        <v>-2.9245</v>
       </c>
       <c r="G22" t="n">
         <v>-5.624</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2368</v>
+        <v>0.2139</v>
       </c>
       <c r="T22" t="n">
         <v>-0.0584</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1783</v>
+        <v>0.2723</v>
       </c>
       <c r="V22" t="n">
         <v>0.3144</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9326</v>
+        <v>-6.2872</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5001</v>
+        <v>-5.1084</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4324</v>
+        <v>-1.1788</v>
       </c>
       <c r="G23" t="n">
         <v>-6.6864</v>
@@ -2248,13 +2248,13 @@
         <v>2.9646</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9874000000000001</v>
+        <v>-0.342</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0943</v>
+        <v>-0.7026</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1069</v>
+        <v>0.3606</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.503</v>
+        <v>-6.8405</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.5682</v>
+        <v>-4.1765</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.9348</v>
+        <v>-2.664</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4546</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.716</v>
+        <v>-0.0535</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6354</v>
+        <v>-0.2437</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0806</v>
+        <v>0.1903</v>
       </c>
       <c r="V24" t="n">
         <v>-2.5177</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.7811</v>
+        <v>-26.1281</v>
       </c>
       <c r="E25" t="n">
-        <v>-13.0535</v>
+        <v>-13.0538</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.7271</v>
+        <v>-13.0742</v>
       </c>
       <c r="G25" t="n">
         <v>-30.57</v>
@@ -2404,13 +2404,13 @@
         <v>18.5286</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6965000000000001</v>
+        <v>1.3493</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.6049</v>
+        <v>-2.6051</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3015</v>
+        <v>3.9542</v>
       </c>
       <c r="V25" t="n">
         <v>0.3132999999999995</v>
